--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.033041409168809</v>
+        <v>1.142869228989932</v>
       </c>
       <c r="D2" t="n">
-        <v>11.42691520532605</v>
+        <v>1.856873720865483</v>
       </c>
       <c r="E2" t="n">
-        <v>8.332694790100689</v>
+        <v>1.354062903391362</v>
       </c>
       <c r="F2" t="n">
-        <v>5.869905810786809</v>
+        <v>0.9538596942528564</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.69843098937018</v>
+        <v>3.850995035772655</v>
       </c>
       <c r="D3" t="n">
-        <v>23.16672682689967</v>
+        <v>3.764593109371196</v>
       </c>
       <c r="E3" t="n">
-        <v>8.332694790100689</v>
+        <v>1.354062903391362</v>
       </c>
       <c r="F3" t="n">
-        <v>5.869905810786809</v>
+        <v>0.9538596942528564</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
